--- a/5. Other/BÁO GIÁ BẢO HÀNH ST/Equipment fault information record sheet_2026.xlsx
+++ b/5. Other/BÁO GIÁ BẢO HÀNH ST/Equipment fault information record sheet_2026.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Device fault Information" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Device fault Information'!$A$2:$AQ$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Device fault Information'!$A$2:$AQ$15</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
   <si>
     <t>Device fault information record form</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>MAC: 0018F56346B5</t>
+  </si>
+  <si>
+    <t>00BD0006B4</t>
+  </si>
+  <si>
+    <t>MAC: 0018F5597F3B</t>
   </si>
 </sst>
 </file>
@@ -256,11 +262,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -273,6 +274,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="宋体"/>
       <charset val="163"/>
     </font>
@@ -432,7 +440,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -484,80 +492,65 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -838,7 +831,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
@@ -847,7 +840,7 @@
     <col min="4" max="4" width="12.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35" style="21" customWidth="1"/>
+    <col min="7" max="7" width="35" style="19" customWidth="1"/>
     <col min="8" max="8" width="23.375" style="1" customWidth="1"/>
     <col min="9" max="10" width="93.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.125" style="1" customWidth="1"/>
@@ -858,23 +851,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="1" customFormat="1" ht="34.15" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
       <c r="P1" s="9"/>
       <c r="Q1" s="9"/>
       <c r="R1" s="9"/>
@@ -923,7 +916,7 @@
       <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="17" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
@@ -981,31 +974,31 @@
       <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="27" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="21"/>
       <c r="K3" s="29"/>
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
@@ -1048,23 +1041,23 @@
       <c r="A4" s="22">
         <v>2</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="26" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="21" t="s">
         <v>46</v>
       </c>
       <c r="G4" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="28"/>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="26"/>
+      <c r="J4" s="21"/>
       <c r="K4" s="29"/>
       <c r="L4" s="30"/>
       <c r="M4" s="30"/>
@@ -1103,21 +1096,23 @@
       <c r="A5" s="22">
         <v>3</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="33" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="26"/>
+      <c r="F5" s="21" t="s">
+        <v>49</v>
+      </c>
       <c r="G5" s="27" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H5" s="28"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="26"/>
+      <c r="J5" s="21"/>
       <c r="K5" s="29"/>
       <c r="L5" s="30"/>
       <c r="M5" s="30"/>
@@ -1156,23 +1151,21 @@
       <c r="A6" s="22">
         <v>4</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="33" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="33" t="s">
-        <v>43</v>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" s="28"/>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="26"/>
+      <c r="J6" s="21"/>
       <c r="K6" s="29"/>
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
@@ -1211,23 +1204,23 @@
       <c r="A7" s="22">
         <v>5</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="33" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>45</v>
+      <c r="F7" s="21" t="s">
+        <v>43</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H7" s="28"/>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="21"/>
       <c r="K7" s="29"/>
       <c r="L7" s="30"/>
       <c r="M7" s="30"/>
@@ -1266,23 +1259,23 @@
       <c r="A8" s="22">
         <v>6</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="33" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="33" t="s">
-        <v>42</v>
+      <c r="F8" s="21" t="s">
+        <v>45</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8" s="28"/>
-      <c r="I8" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="26"/>
+      <c r="I8" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="29"/>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
@@ -1321,23 +1314,23 @@
       <c r="A9" s="22">
         <v>7</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="33" t="s">
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>40</v>
+      <c r="F9" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H9" s="28"/>
-      <c r="I9" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="26"/>
+      <c r="I9" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="21"/>
       <c r="K9" s="29"/>
       <c r="L9" s="30"/>
       <c r="M9" s="30"/>
@@ -1376,26 +1369,26 @@
       <c r="A10" s="22">
         <v>8</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="33" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="33" t="s">
-        <v>41</v>
+      <c r="F10" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="28"/>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="26"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
       <c r="N10" s="31"/>
       <c r="O10" s="32"/>
       <c r="P10" s="9"/>
@@ -1431,26 +1424,26 @@
       <c r="A11" s="22">
         <v>9</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="33" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="33" t="s">
-        <v>44</v>
+      <c r="F11" s="21" t="s">
+        <v>41</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="28"/>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="26"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="31"/>
       <c r="O11" s="32"/>
       <c r="P11" s="9"/>
@@ -1486,23 +1479,23 @@
       <c r="A12" s="22">
         <v>10</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="33" t="s">
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="33" t="s">
-        <v>39</v>
+      <c r="F12" s="21" t="s">
+        <v>44</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12" s="28"/>
-      <c r="I12" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="26"/>
+      <c r="I12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="21"/>
       <c r="K12" s="29"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
@@ -1541,28 +1534,28 @@
       <c r="A13" s="22">
         <v>11</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="33" t="s">
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="33" t="s">
-        <v>38</v>
+      <c r="F13" s="21" t="s">
+        <v>39</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="28"/>
-      <c r="I13" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="26"/>
+      <c r="I13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="29"/>
       <c r="L13" s="30"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="37"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -1592,27 +1585,82 @@
       <c r="AP13" s="9"/>
       <c r="AQ13" s="9"/>
     </row>
-    <row r="14" spans="1:43" ht="13.5" hidden="1" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="16"/>
+    <row r="14" spans="1:43" ht="15.95" customHeight="1">
+      <c r="A14" s="22">
+        <v>12</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="28"/>
+      <c r="I14" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="9"/>
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
+      <c r="AF14" s="9"/>
+      <c r="AG14" s="9"/>
+      <c r="AH14" s="9"/>
+      <c r="AI14" s="9"/>
+      <c r="AJ14" s="9"/>
+      <c r="AK14" s="9"/>
+      <c r="AL14" s="9"/>
+      <c r="AM14" s="9"/>
+      <c r="AN14" s="9"/>
+      <c r="AO14" s="9"/>
+      <c r="AP14" s="9"/>
+      <c r="AQ14" s="9"/>
     </row>
-    <row r="15" spans="1:43" ht="14.1" hidden="1" customHeight="1"/>
+    <row r="15" spans="1:43" ht="13.5" hidden="1" customHeight="1">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="E15" s="14"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:43" ht="14.1" hidden="1" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A2:AQ14"/>
+  <autoFilter ref="A2:AQ15"/>
   <mergeCells count="7">
-    <mergeCell ref="H3:H13"/>
+    <mergeCell ref="H3:H14"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B3:B13"/>
-    <mergeCell ref="D3:D13"/>
-    <mergeCell ref="C3:C13"/>
-    <mergeCell ref="O3:O13"/>
-    <mergeCell ref="N3:N13"/>
+    <mergeCell ref="B3:B14"/>
+    <mergeCell ref="D3:D14"/>
+    <mergeCell ref="C3:C14"/>
+    <mergeCell ref="O3:O14"/>
+    <mergeCell ref="N3:N14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N3" r:id="rId1"/>
